--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_04.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_04.xlsx
@@ -480,25 +480,25 @@
         <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>1482.27</v>
+        <v>1475.36</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1077.94</v>
+        <v>1069.41</v>
       </c>
       <c r="E5" t="n">
-        <v>292.68</v>
+        <v>294.37</v>
       </c>
       <c r="F5" t="n">
-        <v>2421</v>
+        <v>1376</v>
       </c>
       <c r="G5" t="n">
-        <v>411635</v>
+        <v>424135</v>
       </c>
       <c r="H5" t="n">
-        <v>72536</v>
+        <v>63470</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45749</v>
       </c>
       <c r="B6" t="n">
-        <v>548.86</v>
+        <v>553.4</v>
       </c>
       <c r="C6" t="n">
         <v>9.07</v>
       </c>
       <c r="D6" t="n">
-        <v>397.36</v>
+        <v>402.5</v>
       </c>
       <c r="E6" t="n">
-        <v>110.24</v>
+        <v>106.45</v>
       </c>
       <c r="F6" t="n">
-        <v>1060</v>
+        <v>700</v>
       </c>
       <c r="G6" t="n">
-        <v>160851</v>
+        <v>158535</v>
       </c>
       <c r="H6" t="n">
-        <v>24736</v>
+        <v>25670</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45750</v>
       </c>
       <c r="B7" t="n">
-        <v>1524.51</v>
+        <v>1433.52</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1098.79</v>
+        <v>1042.39</v>
       </c>
       <c r="E7" t="n">
-        <v>304.55</v>
+        <v>284.43</v>
       </c>
       <c r="F7" t="n">
-        <v>2413</v>
+        <v>1158</v>
       </c>
       <c r="G7" t="n">
-        <v>379773</v>
+        <v>368178</v>
       </c>
       <c r="H7" t="n">
-        <v>71099</v>
+        <v>65368</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45751</v>
       </c>
       <c r="B8" t="n">
-        <v>1439.88</v>
+        <v>1404.7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.55</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>1048.51</v>
+        <v>1009.91</v>
       </c>
       <c r="E8" t="n">
-        <v>279.95</v>
+        <v>270.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1977</v>
+        <v>1452</v>
       </c>
       <c r="G8" t="n">
-        <v>385466</v>
+        <v>402599</v>
       </c>
       <c r="H8" t="n">
-        <v>66812</v>
+        <v>66301</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45752</v>
       </c>
       <c r="B9" t="n">
-        <v>1519.71</v>
+        <v>1465.22</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1101.48</v>
+        <v>1060.44</v>
       </c>
       <c r="E9" t="n">
-        <v>300.79</v>
+        <v>294.12</v>
       </c>
       <c r="F9" t="n">
-        <v>2243</v>
+        <v>1133</v>
       </c>
       <c r="G9" t="n">
-        <v>395583</v>
+        <v>396894</v>
       </c>
       <c r="H9" t="n">
-        <v>67641</v>
+        <v>71673</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45753</v>
       </c>
       <c r="B10" t="n">
-        <v>1163.38</v>
+        <v>1401.51</v>
       </c>
       <c r="C10" t="n">
-        <v>20.42</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>844.59</v>
+        <v>1002.25</v>
       </c>
       <c r="E10" t="n">
-        <v>226.12</v>
+        <v>279.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1750</v>
+        <v>1107</v>
       </c>
       <c r="G10" t="n">
-        <v>295961</v>
+        <v>347130</v>
       </c>
       <c r="H10" t="n">
-        <v>49627</v>
+        <v>63531</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45754</v>
       </c>
       <c r="B11" t="n">
-        <v>1444.96</v>
+        <v>1608</v>
       </c>
       <c r="C11" t="n">
-        <v>23.39</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1038.78</v>
+        <v>1171.63</v>
       </c>
       <c r="E11" t="n">
-        <v>292.52</v>
+        <v>320.23</v>
       </c>
       <c r="F11" t="n">
-        <v>2313</v>
+        <v>1471</v>
       </c>
       <c r="G11" t="n">
-        <v>355797</v>
+        <v>451891</v>
       </c>
       <c r="H11" t="n">
-        <v>61922</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45755</v>
       </c>
       <c r="B12" t="n">
-        <v>1436.21</v>
+        <v>1473.08</v>
       </c>
       <c r="C12" t="n">
-        <v>23.45</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1037.88</v>
+        <v>1064.51</v>
       </c>
       <c r="E12" t="n">
-        <v>283.5</v>
+        <v>296.49</v>
       </c>
       <c r="F12" t="n">
-        <v>2137</v>
+        <v>1445</v>
       </c>
       <c r="G12" t="n">
-        <v>387539</v>
+        <v>371516</v>
       </c>
       <c r="H12" t="n">
-        <v>66682</v>
+        <v>65314</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45756</v>
       </c>
       <c r="B13" t="n">
-        <v>1480.41</v>
+        <v>1556.24</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1071.37</v>
+        <v>1124.52</v>
       </c>
       <c r="E13" t="n">
-        <v>293.71</v>
+        <v>307.57</v>
       </c>
       <c r="F13" t="n">
-        <v>2618</v>
+        <v>1223</v>
       </c>
       <c r="G13" t="n">
-        <v>382408</v>
+        <v>400502</v>
       </c>
       <c r="H13" t="n">
-        <v>66799</v>
+        <v>72579</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45757</v>
       </c>
       <c r="B14" t="n">
-        <v>1389.71</v>
+        <v>1193.57</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>19.48</v>
       </c>
       <c r="D14" t="n">
-        <v>1000.29</v>
+        <v>869.99</v>
       </c>
       <c r="E14" t="n">
-        <v>274.69</v>
+        <v>231.69</v>
       </c>
       <c r="F14" t="n">
-        <v>2397</v>
+        <v>1103</v>
       </c>
       <c r="G14" t="n">
-        <v>402700</v>
+        <v>342298</v>
       </c>
       <c r="H14" t="n">
-        <v>63980</v>
+        <v>55374</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45758</v>
       </c>
       <c r="B15" t="n">
-        <v>1520.04</v>
+        <v>1420.11</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1106.36</v>
+        <v>1030.36</v>
       </c>
       <c r="E15" t="n">
-        <v>306.96</v>
+        <v>279.8</v>
       </c>
       <c r="F15" t="n">
-        <v>2258</v>
+        <v>1241</v>
       </c>
       <c r="G15" t="n">
-        <v>365740</v>
+        <v>381412</v>
       </c>
       <c r="H15" t="n">
-        <v>70690</v>
+        <v>69022</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>1595.99</v>
+        <v>1537.56</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>23.77</v>
       </c>
       <c r="D16" t="n">
-        <v>1164.25</v>
+        <v>1112.62</v>
       </c>
       <c r="E16" t="n">
-        <v>323.07</v>
+        <v>303.31</v>
       </c>
       <c r="F16" t="n">
-        <v>2191</v>
+        <v>1737</v>
       </c>
       <c r="G16" t="n">
-        <v>448973</v>
+        <v>416490</v>
       </c>
       <c r="H16" t="n">
-        <v>76819</v>
+        <v>67661</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45760</v>
       </c>
       <c r="B17" t="n">
-        <v>1423.6</v>
+        <v>1443.47</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1032.87</v>
+        <v>1044.43</v>
       </c>
       <c r="E17" t="n">
-        <v>277.47</v>
+        <v>281.93</v>
       </c>
       <c r="F17" t="n">
-        <v>3030</v>
+        <v>1474</v>
       </c>
       <c r="G17" t="n">
-        <v>394767</v>
+        <v>397598</v>
       </c>
       <c r="H17" t="n">
-        <v>64282</v>
+        <v>66570</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45761</v>
       </c>
       <c r="B18" t="n">
-        <v>1441.79</v>
+        <v>1382.91</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>1048.75</v>
+        <v>999.17</v>
       </c>
       <c r="E18" t="n">
-        <v>293.82</v>
+        <v>263.21</v>
       </c>
       <c r="F18" t="n">
-        <v>2516</v>
+        <v>1234</v>
       </c>
       <c r="G18" t="n">
-        <v>387465</v>
+        <v>369395</v>
       </c>
       <c r="H18" t="n">
-        <v>64168</v>
+        <v>62684</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45762</v>
       </c>
       <c r="B19" t="n">
-        <v>1406.77</v>
+        <v>1415.21</v>
       </c>
       <c r="C19" t="n">
-        <v>23.48</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1021.25</v>
+        <v>1022.06</v>
       </c>
       <c r="E19" t="n">
-        <v>280.93</v>
+        <v>281.67</v>
       </c>
       <c r="F19" t="n">
-        <v>1917</v>
+        <v>1152</v>
       </c>
       <c r="G19" t="n">
-        <v>394550</v>
+        <v>387861</v>
       </c>
       <c r="H19" t="n">
-        <v>63597</v>
+        <v>66561</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45763</v>
       </c>
       <c r="B20" t="n">
-        <v>1563.92</v>
+        <v>1547.17</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1133.36</v>
+        <v>1115.12</v>
       </c>
       <c r="E20" t="n">
-        <v>314.21</v>
+        <v>317.14</v>
       </c>
       <c r="F20" t="n">
-        <v>2153</v>
+        <v>1531</v>
       </c>
       <c r="G20" t="n">
-        <v>412368</v>
+        <v>384493</v>
       </c>
       <c r="H20" t="n">
-        <v>70099</v>
+        <v>68941</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45764</v>
       </c>
       <c r="B21" t="n">
-        <v>1382.9</v>
+        <v>1378.34</v>
       </c>
       <c r="C21" t="n">
-        <v>22.59</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>1004.95</v>
+        <v>993.99</v>
       </c>
       <c r="E21" t="n">
-        <v>269.39</v>
+        <v>269.89</v>
       </c>
       <c r="F21" t="n">
-        <v>2323</v>
+        <v>1276</v>
       </c>
       <c r="G21" t="n">
-        <v>383018</v>
+        <v>409791</v>
       </c>
       <c r="H21" t="n">
-        <v>65131</v>
+        <v>62148</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45765</v>
       </c>
       <c r="B22" t="n">
-        <v>1475.1</v>
+        <v>1446.52</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>23.86</v>
       </c>
       <c r="D22" t="n">
-        <v>1058.57</v>
+        <v>1052.36</v>
       </c>
       <c r="E22" t="n">
-        <v>296.84</v>
+        <v>283.31</v>
       </c>
       <c r="F22" t="n">
-        <v>1891</v>
+        <v>1578</v>
       </c>
       <c r="G22" t="n">
-        <v>356004</v>
+        <v>400811</v>
       </c>
       <c r="H22" t="n">
-        <v>67021</v>
+        <v>63036</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45766</v>
       </c>
       <c r="B23" t="n">
-        <v>1580.57</v>
+        <v>1433.79</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1137.86</v>
+        <v>1043.29</v>
       </c>
       <c r="E23" t="n">
-        <v>304.52</v>
+        <v>291.51</v>
       </c>
       <c r="F23" t="n">
-        <v>2478</v>
+        <v>1279</v>
       </c>
       <c r="G23" t="n">
-        <v>417979</v>
+        <v>384176</v>
       </c>
       <c r="H23" t="n">
-        <v>72982</v>
+        <v>68579</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45767</v>
       </c>
       <c r="B24" t="n">
-        <v>438.82</v>
+        <v>1509.72</v>
       </c>
       <c r="C24" t="n">
-        <v>6.86</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>317.49</v>
+        <v>1093.11</v>
       </c>
       <c r="E24" t="n">
-        <v>87.31999999999999</v>
+        <v>304.04</v>
       </c>
       <c r="F24" t="n">
-        <v>820</v>
+        <v>1366</v>
       </c>
       <c r="G24" t="n">
-        <v>126561</v>
+        <v>382247</v>
       </c>
       <c r="H24" t="n">
-        <v>19954</v>
+        <v>68287</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45768</v>
       </c>
       <c r="B25" t="n">
-        <v>1464.88</v>
+        <v>1436.41</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23.54</v>
       </c>
       <c r="D25" t="n">
-        <v>1071.18</v>
+        <v>1045.72</v>
       </c>
       <c r="E25" t="n">
-        <v>292.7</v>
+        <v>282.05</v>
       </c>
       <c r="F25" t="n">
-        <v>2396</v>
+        <v>1177</v>
       </c>
       <c r="G25" t="n">
-        <v>396493</v>
+        <v>383690</v>
       </c>
       <c r="H25" t="n">
-        <v>67651</v>
+        <v>64337</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45769</v>
       </c>
       <c r="B26" t="n">
-        <v>1466.91</v>
+        <v>1582.42</v>
       </c>
       <c r="C26" t="n">
-        <v>23.09</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>1053.46</v>
+        <v>1147.14</v>
       </c>
       <c r="E26" t="n">
-        <v>295.83</v>
+        <v>317.96</v>
       </c>
       <c r="F26" t="n">
-        <v>2120</v>
+        <v>1463</v>
       </c>
       <c r="G26" t="n">
-        <v>384143</v>
+        <v>397525</v>
       </c>
       <c r="H26" t="n">
-        <v>64895</v>
+        <v>69771</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45770</v>
       </c>
       <c r="B27" t="n">
-        <v>1508.27</v>
+        <v>1278.44</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>20.35</v>
       </c>
       <c r="D27" t="n">
-        <v>1090.31</v>
+        <v>918.34</v>
       </c>
       <c r="E27" t="n">
-        <v>301.11</v>
+        <v>259.47</v>
       </c>
       <c r="F27" t="n">
-        <v>2969</v>
+        <v>1151</v>
       </c>
       <c r="G27" t="n">
-        <v>396669</v>
+        <v>331865</v>
       </c>
       <c r="H27" t="n">
-        <v>69154</v>
+        <v>56243</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45771</v>
       </c>
       <c r="B28" t="n">
-        <v>1389.85</v>
+        <v>1410.22</v>
       </c>
       <c r="C28" t="n">
-        <v>22.38</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1013.01</v>
+        <v>1022.34</v>
       </c>
       <c r="E28" t="n">
-        <v>272.18</v>
+        <v>273.69</v>
       </c>
       <c r="F28" t="n">
-        <v>1780</v>
+        <v>1261</v>
       </c>
       <c r="G28" t="n">
-        <v>373106</v>
+        <v>385288</v>
       </c>
       <c r="H28" t="n">
-        <v>66009</v>
+        <v>68265</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45772</v>
       </c>
       <c r="B29" t="n">
-        <v>1513.54</v>
+        <v>1384.28</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>21.57</v>
       </c>
       <c r="D29" t="n">
-        <v>1098.4</v>
+        <v>1012.84</v>
       </c>
       <c r="E29" t="n">
-        <v>306.13</v>
+        <v>268.95</v>
       </c>
       <c r="F29" t="n">
-        <v>2140</v>
+        <v>1233</v>
       </c>
       <c r="G29" t="n">
-        <v>404676</v>
+        <v>388760</v>
       </c>
       <c r="H29" t="n">
-        <v>66302</v>
+        <v>61506</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45773</v>
       </c>
       <c r="B30" t="n">
-        <v>1396.53</v>
+        <v>1481.34</v>
       </c>
       <c r="C30" t="n">
-        <v>22.15</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1004.16</v>
+        <v>1078.93</v>
       </c>
       <c r="E30" t="n">
-        <v>274.55</v>
+        <v>300.49</v>
       </c>
       <c r="F30" t="n">
-        <v>2325</v>
+        <v>1256</v>
       </c>
       <c r="G30" t="n">
-        <v>360185</v>
+        <v>410590</v>
       </c>
       <c r="H30" t="n">
-        <v>60677</v>
+        <v>65606</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45774</v>
       </c>
       <c r="B31" t="n">
-        <v>1472.7</v>
+        <v>1608</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1075.41</v>
+        <v>1176.09</v>
       </c>
       <c r="E31" t="n">
-        <v>293.9</v>
+        <v>325.52</v>
       </c>
       <c r="F31" t="n">
-        <v>1676</v>
+        <v>1390</v>
       </c>
       <c r="G31" t="n">
-        <v>372294</v>
+        <v>397768</v>
       </c>
       <c r="H31" t="n">
-        <v>70268</v>
+        <v>73292</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45775</v>
       </c>
       <c r="B32" t="n">
-        <v>1511.66</v>
+        <v>1508.93</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1107.79</v>
+        <v>1087.94</v>
       </c>
       <c r="E32" t="n">
-        <v>307.79</v>
+        <v>300.78</v>
       </c>
       <c r="F32" t="n">
-        <v>2180</v>
+        <v>1455</v>
       </c>
       <c r="G32" t="n">
-        <v>387712</v>
+        <v>426959</v>
       </c>
       <c r="H32" t="n">
-        <v>70229</v>
+        <v>68544</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45776</v>
       </c>
       <c r="B33" t="n">
-        <v>1549.96</v>
+        <v>1608</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>1126.44</v>
+        <v>1167.11</v>
       </c>
       <c r="E33" t="n">
-        <v>313.2</v>
+        <v>314.89</v>
       </c>
       <c r="F33" t="n">
-        <v>2301</v>
+        <v>1482</v>
       </c>
       <c r="G33" t="n">
-        <v>390005</v>
+        <v>434940</v>
       </c>
       <c r="H33" t="n">
-        <v>72165</v>
+        <v>69873</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45777</v>
       </c>
       <c r="B34" t="n">
-        <v>1325.44</v>
+        <v>1488</v>
       </c>
       <c r="C34" t="n">
-        <v>21.31</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>960.0700000000001</v>
+        <v>1079.03</v>
       </c>
       <c r="E34" t="n">
-        <v>255.5</v>
+        <v>292.64</v>
       </c>
       <c r="F34" t="n">
-        <v>2494</v>
+        <v>1599</v>
       </c>
       <c r="G34" t="n">
-        <v>331909</v>
+        <v>394083</v>
       </c>
       <c r="H34" t="n">
-        <v>59831</v>
+        <v>66367</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41859.14</v>
+        <v>42865.44</v>
       </c>
       <c r="C36" t="n">
-        <v>673.7399999999999</v>
+        <v>693.64</v>
       </c>
       <c r="D36" t="n">
-        <v>30342.93</v>
+        <v>31059.54</v>
       </c>
       <c r="E36" t="n">
-        <v>8326.17</v>
+        <v>8497.349999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>65287</v>
+        <v>39503</v>
       </c>
       <c r="G36" t="n">
-        <v>11042330</v>
+        <v>11529420</v>
       </c>
       <c r="H36" t="n">
-        <v>1913758</v>
+        <v>1950599</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_04.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_04.xlsx
@@ -480,25 +480,25 @@
         <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>1475.36</v>
+        <v>1528.86</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1069.41</v>
+        <v>1108.89</v>
       </c>
       <c r="E5" t="n">
-        <v>294.37</v>
+        <v>308.28</v>
       </c>
       <c r="F5" t="n">
-        <v>1376</v>
+        <v>1385</v>
       </c>
       <c r="G5" t="n">
-        <v>424135</v>
+        <v>389560</v>
       </c>
       <c r="H5" t="n">
-        <v>63470</v>
+        <v>67205</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45749</v>
       </c>
       <c r="B6" t="n">
-        <v>553.4</v>
+        <v>534.79</v>
       </c>
       <c r="C6" t="n">
         <v>9.07</v>
       </c>
       <c r="D6" t="n">
-        <v>402.5</v>
+        <v>386.22</v>
       </c>
       <c r="E6" t="n">
-        <v>106.45</v>
+        <v>107.08</v>
       </c>
       <c r="F6" t="n">
-        <v>700</v>
+        <v>590</v>
       </c>
       <c r="G6" t="n">
-        <v>158535</v>
+        <v>136944</v>
       </c>
       <c r="H6" t="n">
-        <v>25670</v>
+        <v>25097</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45750</v>
       </c>
       <c r="B7" t="n">
-        <v>1433.52</v>
+        <v>1537.32</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1042.39</v>
+        <v>1106.99</v>
       </c>
       <c r="E7" t="n">
-        <v>284.43</v>
+        <v>311.21</v>
       </c>
       <c r="F7" t="n">
-        <v>1158</v>
+        <v>1475</v>
       </c>
       <c r="G7" t="n">
-        <v>368178</v>
+        <v>397350</v>
       </c>
       <c r="H7" t="n">
-        <v>65368</v>
+        <v>72350</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45751</v>
       </c>
       <c r="B8" t="n">
-        <v>1404.7</v>
+        <v>1548.38</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>1009.91</v>
+        <v>1128.31</v>
       </c>
       <c r="E8" t="n">
-        <v>270.6</v>
+        <v>305.87</v>
       </c>
       <c r="F8" t="n">
-        <v>1452</v>
+        <v>1814</v>
       </c>
       <c r="G8" t="n">
-        <v>402599</v>
+        <v>380337</v>
       </c>
       <c r="H8" t="n">
-        <v>66301</v>
+        <v>66957</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45752</v>
       </c>
       <c r="B9" t="n">
-        <v>1465.22</v>
+        <v>1418.33</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1060.44</v>
+        <v>1022.12</v>
       </c>
       <c r="E9" t="n">
-        <v>294.12</v>
+        <v>283.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1133</v>
+        <v>1166</v>
       </c>
       <c r="G9" t="n">
-        <v>396894</v>
+        <v>379199</v>
       </c>
       <c r="H9" t="n">
-        <v>71673</v>
+        <v>64903</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45753</v>
       </c>
       <c r="B10" t="n">
-        <v>1401.51</v>
+        <v>1507.84</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1002.25</v>
+        <v>1092.15</v>
       </c>
       <c r="E10" t="n">
-        <v>279.15</v>
+        <v>298.95</v>
       </c>
       <c r="F10" t="n">
-        <v>1107</v>
+        <v>1305</v>
       </c>
       <c r="G10" t="n">
-        <v>347130</v>
+        <v>384268</v>
       </c>
       <c r="H10" t="n">
-        <v>63531</v>
+        <v>68742</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45754</v>
       </c>
       <c r="B11" t="n">
-        <v>1608</v>
+        <v>1347.12</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1171.63</v>
+        <v>983.17</v>
       </c>
       <c r="E11" t="n">
-        <v>320.23</v>
+        <v>265.23</v>
       </c>
       <c r="F11" t="n">
-        <v>1471</v>
+        <v>1181</v>
       </c>
       <c r="G11" t="n">
-        <v>451891</v>
+        <v>383415</v>
       </c>
       <c r="H11" t="n">
-        <v>74026</v>
+        <v>65382</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45755</v>
       </c>
       <c r="B12" t="n">
-        <v>1473.08</v>
+        <v>1551.94</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1064.51</v>
+        <v>1121.14</v>
       </c>
       <c r="E12" t="n">
-        <v>296.49</v>
+        <v>296.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1445</v>
+        <v>1430</v>
       </c>
       <c r="G12" t="n">
-        <v>371516</v>
+        <v>413112</v>
       </c>
       <c r="H12" t="n">
-        <v>65314</v>
+        <v>67207</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45756</v>
       </c>
       <c r="B13" t="n">
-        <v>1556.24</v>
+        <v>1525.28</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1124.52</v>
+        <v>1103.87</v>
       </c>
       <c r="E13" t="n">
-        <v>307.57</v>
+        <v>307.49</v>
       </c>
       <c r="F13" t="n">
-        <v>1223</v>
+        <v>1472</v>
       </c>
       <c r="G13" t="n">
-        <v>400502</v>
+        <v>395261</v>
       </c>
       <c r="H13" t="n">
-        <v>72579</v>
+        <v>70791</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45757</v>
       </c>
       <c r="B14" t="n">
-        <v>1193.57</v>
+        <v>1575.95</v>
       </c>
       <c r="C14" t="n">
-        <v>19.48</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>869.99</v>
+        <v>1135.8</v>
       </c>
       <c r="E14" t="n">
-        <v>231.69</v>
+        <v>308.63</v>
       </c>
       <c r="F14" t="n">
-        <v>1103</v>
+        <v>1184</v>
       </c>
       <c r="G14" t="n">
-        <v>342298</v>
+        <v>435950</v>
       </c>
       <c r="H14" t="n">
-        <v>55374</v>
+        <v>67501</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45758</v>
       </c>
       <c r="B15" t="n">
-        <v>1420.11</v>
+        <v>1440.62</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>23.36</v>
       </c>
       <c r="D15" t="n">
-        <v>1030.36</v>
+        <v>1050.06</v>
       </c>
       <c r="E15" t="n">
-        <v>279.8</v>
+        <v>287.05</v>
       </c>
       <c r="F15" t="n">
-        <v>1241</v>
+        <v>1385</v>
       </c>
       <c r="G15" t="n">
-        <v>381412</v>
+        <v>347161</v>
       </c>
       <c r="H15" t="n">
-        <v>69022</v>
+        <v>65196</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45759</v>
       </c>
       <c r="B16" t="n">
-        <v>1537.56</v>
+        <v>1554.32</v>
       </c>
       <c r="C16" t="n">
-        <v>23.77</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1112.62</v>
+        <v>1136.18</v>
       </c>
       <c r="E16" t="n">
-        <v>303.31</v>
+        <v>311.39</v>
       </c>
       <c r="F16" t="n">
-        <v>1737</v>
+        <v>1262</v>
       </c>
       <c r="G16" t="n">
-        <v>416490</v>
+        <v>429345</v>
       </c>
       <c r="H16" t="n">
-        <v>67661</v>
+        <v>68299</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45760</v>
       </c>
       <c r="B17" t="n">
-        <v>1443.47</v>
+        <v>1489.93</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1044.43</v>
+        <v>1093.26</v>
       </c>
       <c r="E17" t="n">
-        <v>281.93</v>
+        <v>299.62</v>
       </c>
       <c r="F17" t="n">
-        <v>1474</v>
+        <v>1503</v>
       </c>
       <c r="G17" t="n">
-        <v>397598</v>
+        <v>381769</v>
       </c>
       <c r="H17" t="n">
-        <v>66570</v>
+        <v>65856</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45761</v>
       </c>
       <c r="B18" t="n">
-        <v>1382.91</v>
+        <v>1489.34</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>999.17</v>
+        <v>1075.6</v>
       </c>
       <c r="E18" t="n">
-        <v>263.21</v>
+        <v>289.75</v>
       </c>
       <c r="F18" t="n">
-        <v>1234</v>
+        <v>1476</v>
       </c>
       <c r="G18" t="n">
-        <v>369395</v>
+        <v>429060</v>
       </c>
       <c r="H18" t="n">
-        <v>62684</v>
+        <v>69564</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45762</v>
       </c>
       <c r="B19" t="n">
-        <v>1415.21</v>
+        <v>1556.61</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>23.48</v>
       </c>
       <c r="D19" t="n">
-        <v>1022.06</v>
+        <v>1129.33</v>
       </c>
       <c r="E19" t="n">
-        <v>281.67</v>
+        <v>314.55</v>
       </c>
       <c r="F19" t="n">
-        <v>1152</v>
+        <v>1649</v>
       </c>
       <c r="G19" t="n">
-        <v>387861</v>
+        <v>425432</v>
       </c>
       <c r="H19" t="n">
-        <v>66561</v>
+        <v>65968</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45763</v>
       </c>
       <c r="B20" t="n">
-        <v>1547.17</v>
+        <v>1567.43</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1115.12</v>
+        <v>1138.1</v>
       </c>
       <c r="E20" t="n">
-        <v>317.14</v>
+        <v>305.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1531</v>
+        <v>1456</v>
       </c>
       <c r="G20" t="n">
-        <v>384493</v>
+        <v>443428</v>
       </c>
       <c r="H20" t="n">
-        <v>68941</v>
+        <v>70988</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45764</v>
       </c>
       <c r="B21" t="n">
-        <v>1378.34</v>
+        <v>1590.41</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>993.99</v>
+        <v>1148.73</v>
       </c>
       <c r="E21" t="n">
-        <v>269.89</v>
+        <v>317.22</v>
       </c>
       <c r="F21" t="n">
-        <v>1276</v>
+        <v>1553</v>
       </c>
       <c r="G21" t="n">
-        <v>409791</v>
+        <v>395583</v>
       </c>
       <c r="H21" t="n">
-        <v>62148</v>
+        <v>74332</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45765</v>
       </c>
       <c r="B22" t="n">
-        <v>1446.52</v>
+        <v>1260.51</v>
       </c>
       <c r="C22" t="n">
-        <v>23.86</v>
+        <v>22.4</v>
       </c>
       <c r="D22" t="n">
-        <v>1052.36</v>
+        <v>911.14</v>
       </c>
       <c r="E22" t="n">
-        <v>283.31</v>
+        <v>252.16</v>
       </c>
       <c r="F22" t="n">
-        <v>1578</v>
+        <v>1203</v>
       </c>
       <c r="G22" t="n">
-        <v>400811</v>
+        <v>340194</v>
       </c>
       <c r="H22" t="n">
-        <v>63036</v>
+        <v>61967</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45766</v>
       </c>
       <c r="B23" t="n">
-        <v>1433.79</v>
+        <v>1329.23</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1043.29</v>
+        <v>961.35</v>
       </c>
       <c r="E23" t="n">
-        <v>291.51</v>
+        <v>272.48</v>
       </c>
       <c r="F23" t="n">
-        <v>1279</v>
+        <v>1200</v>
       </c>
       <c r="G23" t="n">
-        <v>384176</v>
+        <v>382280</v>
       </c>
       <c r="H23" t="n">
-        <v>68579</v>
+        <v>59204</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45767</v>
       </c>
       <c r="B24" t="n">
-        <v>1509.72</v>
+        <v>1516.79</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>22.93</v>
       </c>
       <c r="D24" t="n">
-        <v>1093.11</v>
+        <v>1108.28</v>
       </c>
       <c r="E24" t="n">
-        <v>304.04</v>
+        <v>300.51</v>
       </c>
       <c r="F24" t="n">
-        <v>1366</v>
+        <v>1712</v>
       </c>
       <c r="G24" t="n">
-        <v>382247</v>
+        <v>394573</v>
       </c>
       <c r="H24" t="n">
-        <v>68287</v>
+        <v>66592</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45768</v>
       </c>
       <c r="B25" t="n">
-        <v>1436.41</v>
+        <v>1554.28</v>
       </c>
       <c r="C25" t="n">
-        <v>23.54</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1045.72</v>
+        <v>1118.59</v>
       </c>
       <c r="E25" t="n">
-        <v>282.05</v>
+        <v>319.32</v>
       </c>
       <c r="F25" t="n">
-        <v>1177</v>
+        <v>1266</v>
       </c>
       <c r="G25" t="n">
-        <v>383690</v>
+        <v>373434</v>
       </c>
       <c r="H25" t="n">
-        <v>64337</v>
+        <v>65631</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45769</v>
       </c>
       <c r="B26" t="n">
-        <v>1582.42</v>
+        <v>947.99</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>15.1</v>
       </c>
       <c r="D26" t="n">
-        <v>1147.14</v>
+        <v>689.92</v>
       </c>
       <c r="E26" t="n">
-        <v>317.96</v>
+        <v>186.05</v>
       </c>
       <c r="F26" t="n">
-        <v>1463</v>
+        <v>1054</v>
       </c>
       <c r="G26" t="n">
-        <v>397525</v>
+        <v>267550</v>
       </c>
       <c r="H26" t="n">
-        <v>69771</v>
+        <v>40520</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45770</v>
       </c>
       <c r="B27" t="n">
-        <v>1278.44</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>20.35</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>918.34</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>259.47</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>331865</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>56243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45771</v>
       </c>
       <c r="B28" t="n">
-        <v>1410.22</v>
+        <v>1392.93</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="D28" t="n">
-        <v>1022.34</v>
+        <v>1023.6</v>
       </c>
       <c r="E28" t="n">
-        <v>273.69</v>
+        <v>275.48</v>
       </c>
       <c r="F28" t="n">
-        <v>1261</v>
+        <v>1158</v>
       </c>
       <c r="G28" t="n">
-        <v>385288</v>
+        <v>385653</v>
       </c>
       <c r="H28" t="n">
-        <v>68265</v>
+        <v>59164</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45772</v>
       </c>
       <c r="B29" t="n">
-        <v>1384.28</v>
+        <v>1510.54</v>
       </c>
       <c r="C29" t="n">
-        <v>21.57</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>1012.84</v>
+        <v>1101.47</v>
       </c>
       <c r="E29" t="n">
-        <v>268.95</v>
+        <v>295.41</v>
       </c>
       <c r="F29" t="n">
-        <v>1233</v>
+        <v>1315</v>
       </c>
       <c r="G29" t="n">
-        <v>388760</v>
+        <v>411265</v>
       </c>
       <c r="H29" t="n">
-        <v>61506</v>
+        <v>65968</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45773</v>
       </c>
       <c r="B30" t="n">
-        <v>1481.34</v>
+        <v>1492.45</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1078.93</v>
+        <v>1085.67</v>
       </c>
       <c r="E30" t="n">
-        <v>300.49</v>
+        <v>297</v>
       </c>
       <c r="F30" t="n">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="G30" t="n">
-        <v>410590</v>
+        <v>359639</v>
       </c>
       <c r="H30" t="n">
-        <v>65606</v>
+        <v>71860</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45774</v>
       </c>
       <c r="B31" t="n">
-        <v>1608</v>
+        <v>1509.02</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1176.09</v>
+        <v>1093.46</v>
       </c>
       <c r="E31" t="n">
-        <v>325.52</v>
+        <v>303.22</v>
       </c>
       <c r="F31" t="n">
-        <v>1390</v>
+        <v>1214</v>
       </c>
       <c r="G31" t="n">
-        <v>397768</v>
+        <v>377055</v>
       </c>
       <c r="H31" t="n">
-        <v>73292</v>
+        <v>70742</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45775</v>
       </c>
       <c r="B32" t="n">
-        <v>1508.93</v>
+        <v>1430.27</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>22.78</v>
       </c>
       <c r="D32" t="n">
-        <v>1087.94</v>
+        <v>1039.01</v>
       </c>
       <c r="E32" t="n">
-        <v>300.78</v>
+        <v>275.52</v>
       </c>
       <c r="F32" t="n">
-        <v>1455</v>
+        <v>1124</v>
       </c>
       <c r="G32" t="n">
-        <v>426959</v>
+        <v>388093</v>
       </c>
       <c r="H32" t="n">
-        <v>68544</v>
+        <v>65464</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45776</v>
       </c>
       <c r="B33" t="n">
-        <v>1608</v>
+        <v>1474.49</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>1167.11</v>
+        <v>1061.82</v>
       </c>
       <c r="E33" t="n">
-        <v>314.89</v>
+        <v>285.59</v>
       </c>
       <c r="F33" t="n">
-        <v>1482</v>
+        <v>1027</v>
       </c>
       <c r="G33" t="n">
-        <v>434940</v>
+        <v>371533</v>
       </c>
       <c r="H33" t="n">
-        <v>69873</v>
+        <v>66494</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45777</v>
       </c>
       <c r="B34" t="n">
-        <v>1488</v>
+        <v>1409.15</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1079.03</v>
+        <v>1024.85</v>
       </c>
       <c r="E34" t="n">
-        <v>292.64</v>
+        <v>275.73</v>
       </c>
       <c r="F34" t="n">
-        <v>1599</v>
+        <v>1348</v>
       </c>
       <c r="G34" t="n">
-        <v>394083</v>
+        <v>379937</v>
       </c>
       <c r="H34" t="n">
-        <v>66367</v>
+        <v>63787</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>42865.44</v>
+        <v>41592.11999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>693.64</v>
+        <v>666.02</v>
       </c>
       <c r="D36" t="n">
-        <v>31059.54</v>
+        <v>30179.08</v>
       </c>
       <c r="E36" t="n">
-        <v>8497.349999999999</v>
+        <v>8255.83</v>
       </c>
       <c r="F36" t="n">
-        <v>39503</v>
+        <v>38170</v>
       </c>
       <c r="G36" t="n">
-        <v>11529420</v>
+        <v>10978380</v>
       </c>
       <c r="H36" t="n">
-        <v>1950599</v>
+        <v>1873731</v>
       </c>
     </row>
   </sheetData>
